--- a/artfynd/A 40397-2023 artfynd.xlsx
+++ b/artfynd/A 40397-2023 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119559123</v>
+        <v>119558994</v>
       </c>
       <c r="B3" t="n">
-        <v>74630</v>
+        <v>90527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539156</v>
+        <v>539331</v>
       </c>
       <c r="R3" t="n">
-        <v>7092421</v>
+        <v>7092533</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119558994</v>
+        <v>119559123</v>
       </c>
       <c r="B4" t="n">
-        <v>90527</v>
+        <v>74630</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539331</v>
+        <v>539156</v>
       </c>
       <c r="R4" t="n">
-        <v>7092533</v>
+        <v>7092421</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119559168</v>
+        <v>119558847</v>
       </c>
       <c r="B8" t="n">
-        <v>79607</v>
+        <v>79608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539191</v>
+        <v>539475</v>
       </c>
       <c r="R8" t="n">
-        <v>7092404</v>
+        <v>7092674</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1418,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119558847</v>
+        <v>119559168</v>
       </c>
       <c r="B9" t="n">
-        <v>79608</v>
+        <v>79607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,21 +1434,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539475</v>
+        <v>539191</v>
       </c>
       <c r="R9" t="n">
-        <v>7092674</v>
+        <v>7092404</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1524,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119559054</v>
+        <v>119558939</v>
       </c>
       <c r="B10" t="n">
-        <v>74638</v>
+        <v>90846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,21 +1540,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539197</v>
+        <v>539347</v>
       </c>
       <c r="R10" t="n">
-        <v>7092462</v>
+        <v>7092554</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1630,10 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119558887</v>
+        <v>119559054</v>
       </c>
       <c r="B11" t="n">
-        <v>79607</v>
+        <v>74638</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,21 +1646,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539423</v>
+        <v>539197</v>
       </c>
       <c r="R11" t="n">
-        <v>7092639</v>
+        <v>7092462</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1736,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119558939</v>
+        <v>119558887</v>
       </c>
       <c r="B12" t="n">
-        <v>90846</v>
+        <v>79607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,21 +1752,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539347</v>
+        <v>539423</v>
       </c>
       <c r="R12" t="n">
-        <v>7092554</v>
+        <v>7092639</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>

--- a/artfynd/A 40397-2023 artfynd.xlsx
+++ b/artfynd/A 40397-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119558897</v>
+        <v>119558994</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539460</v>
+        <v>539331</v>
       </c>
       <c r="R2" t="n">
-        <v>7092630</v>
+        <v>7092533</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119558994</v>
+        <v>119558846</v>
       </c>
       <c r="B3" t="n">
-        <v>90527</v>
+        <v>79607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539331</v>
+        <v>539475</v>
       </c>
       <c r="R3" t="n">
-        <v>7092533</v>
+        <v>7092674</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119559123</v>
+        <v>119559054</v>
       </c>
       <c r="B4" t="n">
-        <v>74630</v>
+        <v>74638</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539156</v>
+        <v>539197</v>
       </c>
       <c r="R4" t="n">
-        <v>7092421</v>
+        <v>7092462</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119559076</v>
+        <v>119558939</v>
       </c>
       <c r="B5" t="n">
-        <v>82305</v>
+        <v>90846</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539136</v>
+        <v>539347</v>
       </c>
       <c r="R5" t="n">
-        <v>7092455</v>
+        <v>7092554</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119558853</v>
+        <v>119558897</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>90562</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539450</v>
+        <v>539460</v>
       </c>
       <c r="R6" t="n">
-        <v>7092657</v>
+        <v>7092630</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119558920</v>
+        <v>119559152</v>
       </c>
       <c r="B7" t="n">
-        <v>98242</v>
+        <v>91494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,27 +1221,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219880</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1249,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539372</v>
+        <v>539110</v>
       </c>
       <c r="R7" t="n">
-        <v>7092551</v>
+        <v>7092403</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1312,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119558847</v>
+        <v>119559123</v>
       </c>
       <c r="B8" t="n">
-        <v>79608</v>
+        <v>74630</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539475</v>
+        <v>539156</v>
       </c>
       <c r="R8" t="n">
-        <v>7092674</v>
+        <v>7092421</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1418,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119559168</v>
+        <v>119559076</v>
       </c>
       <c r="B9" t="n">
-        <v>79607</v>
+        <v>82305</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539191</v>
+        <v>539136</v>
       </c>
       <c r="R9" t="n">
-        <v>7092404</v>
+        <v>7092455</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1524,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119558939</v>
+        <v>119558887</v>
       </c>
       <c r="B10" t="n">
-        <v>90846</v>
+        <v>79607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1567,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539347</v>
+        <v>539423</v>
       </c>
       <c r="R10" t="n">
-        <v>7092554</v>
+        <v>7092639</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1630,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119559054</v>
+        <v>119559103</v>
       </c>
       <c r="B11" t="n">
-        <v>74638</v>
+        <v>74622</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1642,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539197</v>
+        <v>539160</v>
       </c>
       <c r="R11" t="n">
-        <v>7092462</v>
+        <v>7092436</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1736,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119558887</v>
+        <v>119558853</v>
       </c>
       <c r="B12" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1779,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539423</v>
+        <v>539450</v>
       </c>
       <c r="R12" t="n">
-        <v>7092639</v>
+        <v>7092657</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1842,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119558846</v>
+        <v>119558970</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
+        <v>90846</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1885,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539475</v>
+        <v>539331</v>
       </c>
       <c r="R13" t="n">
-        <v>7092674</v>
+        <v>7092533</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1948,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119558906</v>
+        <v>119558847</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>79608</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1991,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539412</v>
+        <v>539475</v>
       </c>
       <c r="R14" t="n">
-        <v>7092603</v>
+        <v>7092674</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2054,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119559103</v>
+        <v>119559109</v>
       </c>
       <c r="B15" t="n">
-        <v>74622</v>
+        <v>90562</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2066,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2100,7 +2099,7 @@
         <v>539160</v>
       </c>
       <c r="R15" t="n">
-        <v>7092436</v>
+        <v>7092433</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2160,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119559152</v>
+        <v>119558920</v>
       </c>
       <c r="B16" t="n">
-        <v>91494</v>
+        <v>98242</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2176,26 +2175,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>219880</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>539110</v>
+        <v>539372</v>
       </c>
       <c r="R16" t="n">
-        <v>7092403</v>
+        <v>7092551</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2266,10 +2266,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119558970</v>
+        <v>119558906</v>
       </c>
       <c r="B17" t="n">
-        <v>90846</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,21 +2282,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>539331</v>
+        <v>539412</v>
       </c>
       <c r="R17" t="n">
-        <v>7092533</v>
+        <v>7092603</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119559109</v>
+        <v>119559168</v>
       </c>
       <c r="B18" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,21 +2388,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>539160</v>
+        <v>539191</v>
       </c>
       <c r="R18" t="n">
-        <v>7092433</v>
+        <v>7092404</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>

--- a/artfynd/A 40397-2023 artfynd.xlsx
+++ b/artfynd/A 40397-2023 artfynd.xlsx
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119558920</v>
+        <v>119558906</v>
       </c>
       <c r="B16" t="n">
-        <v>98242</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,31 +2171,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219880</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2203,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>539372</v>
+        <v>539412</v>
       </c>
       <c r="R16" t="n">
-        <v>7092551</v>
+        <v>7092603</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2266,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119558906</v>
+        <v>119558920</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>98242</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2278,30 +2277,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>219880</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>539412</v>
+        <v>539372</v>
       </c>
       <c r="R17" t="n">
-        <v>7092603</v>
+        <v>7092551</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 40397-2023 artfynd.xlsx
+++ b/artfynd/A 40397-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119558994</v>
+        <v>119559054</v>
       </c>
       <c r="B2" t="n">
-        <v>90527</v>
+        <v>74638</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539331</v>
+        <v>539197</v>
       </c>
       <c r="R2" t="n">
-        <v>7092533</v>
+        <v>7092462</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119558846</v>
+        <v>119558847</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>79608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119559054</v>
+        <v>119558906</v>
       </c>
       <c r="B4" t="n">
-        <v>74638</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539197</v>
+        <v>539412</v>
       </c>
       <c r="R4" t="n">
-        <v>7092462</v>
+        <v>7092603</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119558939</v>
+        <v>119558994</v>
       </c>
       <c r="B5" t="n">
-        <v>90846</v>
+        <v>90527</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539347</v>
+        <v>539331</v>
       </c>
       <c r="R5" t="n">
-        <v>7092554</v>
+        <v>7092533</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119558897</v>
+        <v>119558887</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539460</v>
+        <v>539423</v>
       </c>
       <c r="R6" t="n">
-        <v>7092630</v>
+        <v>7092639</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119559152</v>
+        <v>119559109</v>
       </c>
       <c r="B7" t="n">
-        <v>91494</v>
+        <v>90562</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539110</v>
+        <v>539160</v>
       </c>
       <c r="R7" t="n">
-        <v>7092403</v>
+        <v>7092433</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119559123</v>
+        <v>119559103</v>
       </c>
       <c r="B8" t="n">
-        <v>74630</v>
+        <v>74622</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>6439</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539156</v>
+        <v>539160</v>
       </c>
       <c r="R8" t="n">
-        <v>7092421</v>
+        <v>7092436</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119559076</v>
+        <v>119559123</v>
       </c>
       <c r="B9" t="n">
-        <v>82305</v>
+        <v>74630</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539136</v>
+        <v>539156</v>
       </c>
       <c r="R9" t="n">
-        <v>7092455</v>
+        <v>7092421</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119558887</v>
+        <v>119558920</v>
       </c>
       <c r="B10" t="n">
-        <v>79607</v>
+        <v>98242</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,30 +1535,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1566,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539423</v>
+        <v>539372</v>
       </c>
       <c r="R10" t="n">
-        <v>7092639</v>
+        <v>7092551</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1629,10 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119559103</v>
+        <v>119559168</v>
       </c>
       <c r="B11" t="n">
-        <v>74622</v>
+        <v>79607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1642,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1672,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539160</v>
+        <v>539191</v>
       </c>
       <c r="R11" t="n">
-        <v>7092436</v>
+        <v>7092404</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1841,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119558970</v>
+        <v>119559152</v>
       </c>
       <c r="B13" t="n">
-        <v>90846</v>
+        <v>91494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1854,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1884,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539331</v>
+        <v>539110</v>
       </c>
       <c r="R13" t="n">
-        <v>7092533</v>
+        <v>7092403</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1947,10 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119558847</v>
+        <v>119558939</v>
       </c>
       <c r="B14" t="n">
-        <v>79608</v>
+        <v>90846</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1964,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1990,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539475</v>
+        <v>539347</v>
       </c>
       <c r="R14" t="n">
-        <v>7092674</v>
+        <v>7092554</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2053,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119559109</v>
+        <v>119559076</v>
       </c>
       <c r="B15" t="n">
-        <v>90562</v>
+        <v>82305</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2070,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539160</v>
+        <v>539136</v>
       </c>
       <c r="R15" t="n">
-        <v>7092433</v>
+        <v>7092455</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2159,10 +2160,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119558906</v>
+        <v>119558846</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>79607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,21 +2176,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2202,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>539412</v>
+        <v>539475</v>
       </c>
       <c r="R16" t="n">
-        <v>7092603</v>
+        <v>7092674</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2265,10 +2266,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119558920</v>
+        <v>119558897</v>
       </c>
       <c r="B17" t="n">
-        <v>98242</v>
+        <v>90562</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,31 +2278,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219880</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>539372</v>
+        <v>539460</v>
       </c>
       <c r="R17" t="n">
-        <v>7092551</v>
+        <v>7092630</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119559168</v>
+        <v>119558970</v>
       </c>
       <c r="B18" t="n">
-        <v>79607</v>
+        <v>90846</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,21 +2388,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>539191</v>
+        <v>539331</v>
       </c>
       <c r="R18" t="n">
-        <v>7092404</v>
+        <v>7092533</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>

--- a/artfynd/A 40397-2023 artfynd.xlsx
+++ b/artfynd/A 40397-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119559054</v>
+        <v>119559123</v>
       </c>
       <c r="B2" t="n">
-        <v>74638</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539197</v>
+        <v>539156</v>
       </c>
       <c r="R2" t="n">
-        <v>7092462</v>
+        <v>7092421</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,42 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119558847</v>
+        <v>119558839</v>
       </c>
       <c r="B3" t="n">
-        <v>79608</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539475</v>
+        <v>539465</v>
       </c>
       <c r="R3" t="n">
-        <v>7092674</v>
+        <v>7092679</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119558906</v>
+        <v>119558939</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539412</v>
+        <v>539347</v>
       </c>
       <c r="R4" t="n">
-        <v>7092603</v>
+        <v>7092554</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,37 +979,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119558994</v>
+        <v>119558970</v>
       </c>
       <c r="B5" t="n">
-        <v>90527</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1099,15 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119558887</v>
+        <v>119558897</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1091,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539423</v>
+        <v>539460</v>
       </c>
       <c r="R6" t="n">
-        <v>7092639</v>
+        <v>7092630</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,12 +1184,7 @@
         <v>119559109</v>
       </c>
       <c r="B7" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,37 +1282,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119559103</v>
+        <v>119559076</v>
       </c>
       <c r="B8" t="n">
-        <v>74622</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6439</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539160</v>
+        <v>539136</v>
       </c>
       <c r="R8" t="n">
-        <v>7092436</v>
+        <v>7092455</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1417,15 +1383,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119559123</v>
+        <v>119558847</v>
       </c>
       <c r="B9" t="n">
-        <v>74630</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,21 +1394,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>308</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539156</v>
+        <v>539475</v>
       </c>
       <c r="R9" t="n">
-        <v>7092421</v>
+        <v>7092674</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1523,15 +1484,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119558920</v>
+        <v>119559152</v>
       </c>
       <c r="B10" t="n">
-        <v>98242</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1539,27 +1495,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219880</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1567,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539372</v>
+        <v>539110</v>
       </c>
       <c r="R10" t="n">
-        <v>7092551</v>
+        <v>7092403</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1630,37 +1585,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119559168</v>
+        <v>119558994</v>
       </c>
       <c r="B11" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539191</v>
+        <v>539331</v>
       </c>
       <c r="R11" t="n">
-        <v>7092404</v>
+        <v>7092533</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1736,37 +1686,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119558853</v>
+        <v>119558841</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1779,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>539450</v>
+        <v>539468</v>
       </c>
       <c r="R12" t="n">
-        <v>7092657</v>
+        <v>7092681</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1842,15 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119559152</v>
+        <v>119559103</v>
       </c>
       <c r="B13" t="n">
-        <v>91494</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,21 +1798,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>6439</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1885,10 +1825,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>539110</v>
+        <v>539160</v>
       </c>
       <c r="R13" t="n">
-        <v>7092403</v>
+        <v>7092436</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1948,15 +1888,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119558939</v>
+        <v>119559054</v>
       </c>
       <c r="B14" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,21 +1899,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1991,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>539347</v>
+        <v>539197</v>
       </c>
       <c r="R14" t="n">
-        <v>7092554</v>
+        <v>7092462</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2054,15 +1989,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119559076</v>
+        <v>119558846</v>
       </c>
       <c r="B15" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2070,21 +2000,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2097,10 +2027,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>539136</v>
+        <v>539475</v>
       </c>
       <c r="R15" t="n">
-        <v>7092455</v>
+        <v>7092674</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2160,15 +2090,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119558846</v>
+        <v>119558887</v>
       </c>
       <c r="B16" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>539475</v>
+        <v>539423</v>
       </c>
       <c r="R16" t="n">
-        <v>7092674</v>
+        <v>7092639</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2266,15 +2191,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119558897</v>
+        <v>119559168</v>
       </c>
       <c r="B17" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2282,21 +2202,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2309,10 +2229,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>539460</v>
+        <v>539191</v>
       </c>
       <c r="R17" t="n">
-        <v>7092630</v>
+        <v>7092404</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2372,42 +2292,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119558970</v>
+        <v>119558920</v>
       </c>
       <c r="B18" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>219880</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2415,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>539331</v>
+        <v>539372</v>
       </c>
       <c r="R18" t="n">
-        <v>7092533</v>
+        <v>7092551</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>

--- a/artfynd/A 40397-2023 artfynd.xlsx
+++ b/artfynd/A 40397-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119559123</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119558839</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119558939</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119558970</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119558897</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119559109</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119559076</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1481,6 +1521,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119558847</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1582,6 +1627,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119559152</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1683,6 +1733,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119558994</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1784,6 +1839,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119558841</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1885,6 +1945,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119559103</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1986,6 +2051,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119559054</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2087,6 +2157,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119558846</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2188,6 +2263,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119558887</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2289,6 +2369,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119559168</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2391,8 +2476,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119558920</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>